--- a/docs/submission/figures_for_review/Table_1.xlsx
+++ b/docs/submission/figures_for_review/Table_1.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Fig 1D</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Fig 1E</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
-          <t>Fig 3E</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>Fig 3E</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>Fig 3E</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Fig 5A</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fig 1D</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Fig 5B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Fig 5C</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Fig S7</t>
+          <t>Fig S4</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Fig S7</t>
+          <t>Fig S4</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Fig 3A</t>
+          <t>Fig 3</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Fig 3B</t>
+          <t>Fig 3</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Fig 3C</t>
+          <t>Fig 3</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Fig S4A</t>
+          <t>Table S4</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Fig 4C</t>
+          <t>Fig 2B</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Fig 4D</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Fig S6</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Fig S6</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Fig 6B</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Fig 6B</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Fig 7A</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Fig 7A</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Fig 7B</t>
+          <t>S1 Text</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Fig S5</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Fig S4B</t>
+          <t>Table S3</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fig S2C</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fig S2C</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>Ranking recovery ceiling</t>
+          <t>Ranking recovery ceiling (calibrated signal)</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="G60" s="24" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="24" t="inlineStr">
         <is>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>S2 Text</t>
         </is>
       </c>
     </row>
     <row r="63" ht="150" customHeight="1">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>Bonferroni correction applied over the k = 52 principal inferential tests (k = 52 = 61 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is reported as a pass-rate (5 of 6 under CellMarker, 6 of 6 under the held-out HPA reference; Figure S6, Methods), not as a single inventory p-value. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 61 tests. Intermediate unharmonized values discussed in the manuscript text are documented in Table S4 rather than the unified test inventory.</t>
+          <t>Bonferroni correction applied over the k = 52 principal inferential tests (k = 52 = 61 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is reported as a pass-rate (5 of 6 under CellMarker, 6 of 6 under the held-out HPA reference; Figure S6, Methods), not as a single inventory p-value. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 61 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 52 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. Intermediate unharmonized values discussed in the manuscript text are documented in Table S4 rather than the unified test inventory.</t>
         </is>
       </c>
     </row>

--- a/docs/submission/figures_for_review/Table_1.xlsx
+++ b/docs/submission/figures_for_review/Table_1.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Fig S1A</t>
+          <t>S1 Fig A</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Fig S1B</t>
+          <t>S1 Fig B</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Fig S4</t>
+          <t>S4 Fig</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Fig S4</t>
+          <t>S4 Fig</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Fig S2E</t>
+          <t>S2 Fig E</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Fig S2F</t>
+          <t>S2 Fig F</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Fig S2F</t>
+          <t>S2 Fig F</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Fig S2F</t>
+          <t>S2 Fig F</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Table S4</t>
+          <t>S4 Table</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Table S1</t>
+          <t>S1 Table</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Table S3</t>
+          <t>S3 Table</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>Fig S3B</t>
+          <t>S3 Fig B</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Fig S2C</t>
+          <t>S2 Fig C</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Fig S2C</t>
+          <t>S2 Fig C</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Fig S2C</t>
+          <t>S2 Fig C</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Fig S1F</t>
+          <t>S1 Fig F</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K60" s="24" t="inlineStr">
         <is>
-          <t>Fig S1D</t>
+          <t>S1 Fig D</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Fig S1E</t>
+          <t>S1 Fig E</t>
         </is>
       </c>
     </row>

--- a/docs/submission/figures_for_review/Table_1.xlsx
+++ b/docs/submission/figures_for_review/Table_1.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Bonferroni p
-(k=52)</t>
+(k=55)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>&lt; 5.2e-5</t>
+          <t>&lt; 5.5e-5</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
         <v>0.0001</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>&lt; 5.2e-5</t>
+          <t>&lt; 5.5e-5</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>&lt; 5.2e-12</t>
+          <t>&lt; 5.5e-12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>&lt; 0.052</t>
+          <t>&lt; 0.055</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>&lt; 0.052</t>
+          <t>&lt; 0.055</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
         <v>0.0043</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.2236</v>
+        <v>0.2365</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>0.0001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>0.013</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.676</v>
+        <v>0.715</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>0.008800000000000001</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.4576</v>
+        <v>0.484</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>0.0035</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.182</v>
+        <v>0.1925</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>0.0001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>0.0001</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>0.0001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.0001</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>0.0001</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>0.019</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>2.1e-13</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>1.092e-11</v>
+        <v>1.155e-11</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>1.15e-12</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>5.98e-11</v>
+        <v>6.325e-11</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>8.9e-11</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>4.628e-09</v>
+        <v>4.895e-09</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>0.01</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>0.0001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0055</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -3709,16 +3709,160 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="150" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>Bonferroni correction applied over the k = 52 principal inferential tests (k = 52 = 61 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is reported as a pass-rate (5 of 6 under CellMarker, 6 of 6 under the held-out HPA reference; Figure S6, Methods), not as a single inventory p-value. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 61 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 52 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. Intermediate unharmonized values discussed in the manuscript text are documented in Table S4 rather than the unified test inventory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1"/>
-    <row r="65" ht="85" customHeight="1"/>
-    <row r="66" ht="90" customHeight="1"/>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>T67</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Global coherence</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Marker-similarity-stratified null (Ward K = 15)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Label permutation (stratified)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>obs/null</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="H63" s="23" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>S5 Fig A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Ranking validation</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Per-type residual vs marker-distinctness</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="H64" s="23" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Exploratory</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>S5 Fig B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>T69</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Two-layer</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Layer 2 PanSci replication (Krzanowski S, k=5, pre-rotation)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Label permutation</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Krzanowski S</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="H65" s="23" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Confirmatory</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>S2 Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="150" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>Bonferroni correction applied over the k = 55 principal inferential tests (k = 55 = 64 − 9). The 9 excluded IDs (T03, T04, T09, T10, T18, T62, T63, T64, T65) are descriptive, aggregate, or diagnostic quantities that make no inferential significance claim and are therefore not part of the multiple-testing family. Green rows = confirmatory; yellow rows = exploratory or diagnostic. Status definitions: Confirmatory = pre-specified or direct replication; Exploratory = post-hoc, respecified, or hypothesis-generating; Diagnostic = simulation calibration (no inferential claim). T44: individual Fisher p-values for 6 niche gene sets (0.045, 0.069, 0.112, 0.761, 1.0, 1.0; all q &gt; 0.05 after FDR). T47: 11 expression-level sub-tests, all |ρ| &lt; 0.21, all p &gt; 0.2. T48: best of 27 metric-threshold combinations (ρ = 0.291, p = 0.090, FDR q = 0.756). T34/T35: the inventoried fold-enrichments are for the overall 500-gene identity set; the per-type top-50 centroid-deviation test on the 6 validation types is reported as a pass-rate (5 of 6 under CellMarker, 6 of 6 under the held-out HPA reference; Figure S6, Methods), not as a single inventory p-value. T29, T54, and the T55-T57 treeness tests are intentionally absent (T29/T54 from an earlier refactor; treeness panels cut); the inventory totals 64 tests. The nine excluded IDs are the rows carrying an em-dash in the Bonferroni p column. T11 is inside the family of 55 but reports a resampling confidence interval rather than a p-value, so it carries no corrected p; its direction robustness is given in that column instead. T44, T47 and T48 also report a raw p as a range or a bound over several sub-tests rather than as a single value, but each is corrected and capped like any other in-family row. Intermediate unharmonized values discussed in the manuscript text are documented in Table S4 rather than the unified test inventory.</t>
+        </is>
+      </c>
+    </row>
     <row r="67" ht="16" customHeight="1"/>
     <row r="68" ht="16" customHeight="1"/>
     <row r="69" ht="16" customHeight="1"/>
@@ -3734,7 +3878,7 @@
   <autoFilter ref="A1:K76"/>
   <mergeCells count="2">
     <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A69:K69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
